--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>127025164</v>
       </c>
       <c r="B10" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>127025162</v>
       </c>
       <c r="B11" t="n">
-        <v>88654</v>
+        <v>88722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,32 +1713,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127025154</v>
+        <v>127025168</v>
       </c>
       <c r="B12" t="n">
-        <v>98395</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633966</v>
+        <v>633757</v>
       </c>
       <c r="R12" t="n">
-        <v>6963757</v>
+        <v>6963816</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1797,7 +1797,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ã„ldre ringhack pÃ¥ tvÃ¥ tallar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,32 +1829,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127025168</v>
+        <v>127025154</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1863,10 +1868,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633757</v>
+        <v>633966</v>
       </c>
       <c r="R13" t="n">
-        <v>6963816</v>
+        <v>6963757</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,7 +1903,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1908,12 +1913,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ã„ldre ringhack pÃ¥ tvÃ¥ tallar</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1943,7 +1943,7 @@
         <v>127025163</v>
       </c>
       <c r="B14" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127025160</v>
+        <v>127025155</v>
       </c>
       <c r="B15" t="n">
-        <v>98395</v>
+        <v>98457</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,16 +2062,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219874</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633926</v>
+        <v>633773</v>
       </c>
       <c r="R15" t="n">
-        <v>6963802</v>
+        <v>6964115</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025155</v>
+        <v>127025160</v>
       </c>
       <c r="B17" t="n">
-        <v>98382</v>
+        <v>98470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,16 +2289,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633773</v>
+        <v>633926</v>
       </c>
       <c r="R17" t="n">
-        <v>6964115</v>
+        <v>6963802</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,37 +2389,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127025170</v>
+        <v>127025156</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>98436</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>634032</v>
+        <v>633678</v>
       </c>
       <c r="R18" t="n">
-        <v>6963951</v>
+        <v>6964104</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2458,27 +2458,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>TvÃ¥ individer i luven pÃ¥ varandra.</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,37 +2500,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127025156</v>
+        <v>127025170</v>
       </c>
       <c r="B19" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2544,13 +2539,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633678</v>
+        <v>634032</v>
       </c>
       <c r="R19" t="n">
-        <v>6964104</v>
+        <v>6963951</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2574,22 +2569,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>TvÃ¥ individer i luven pÃ¥ varandra.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,7 +2619,7 @@
         <v>127025158</v>
       </c>
       <c r="B20" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127025311</v>
+        <v>127025161</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>88722</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,37 +2738,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skälansjön, Ång</t>
+          <t>GÃ¥ltjÃ¤rn, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633851</v>
+        <v>633930</v>
       </c>
       <c r="R21" t="n">
-        <v>6963748</v>
+        <v>6963796</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2792,17 +2796,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,7 +2838,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127025310</v>
+        <v>127025311</v>
       </c>
       <c r="B22" t="n">
         <v>57657</v>
@@ -2864,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633825</v>
+        <v>633851</v>
       </c>
       <c r="R22" t="n">
-        <v>6963994</v>
+        <v>6963748</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2904,7 +2913,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska + äldre ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2931,10 +2940,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127025161</v>
+        <v>127025310</v>
       </c>
       <c r="B23" t="n">
-        <v>88654</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,41 +2951,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>GÃ¥ltjÃ¤rn, Ång</t>
+          <t>Skälansjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633930</v>
+        <v>633825</v>
       </c>
       <c r="R23" t="n">
-        <v>6963796</v>
+        <v>6963994</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3000,22 +3005,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska + äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3379,7 +3379,7 @@
         <v>127025165</v>
       </c>
       <c r="B27" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>127025164</v>
       </c>
       <c r="B10" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>127025162</v>
       </c>
       <c r="B11" t="n">
-        <v>88722</v>
+        <v>88728</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>127025154</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>127025163</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,37 +2051,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127025155</v>
+        <v>127025167</v>
       </c>
       <c r="B15" t="n">
-        <v>98457</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633773</v>
+        <v>633769</v>
       </c>
       <c r="R15" t="n">
-        <v>6964115</v>
+        <v>6963779</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2135,7 +2135,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>FÃ¤rska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,32 +2167,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127025167</v>
+        <v>127025160</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>98476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2201,13 +2206,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633769</v>
+        <v>633926</v>
       </c>
       <c r="R16" t="n">
-        <v>6963779</v>
+        <v>6963802</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2236,7 +2241,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2246,12 +2251,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>FÃ¤rska ringhack</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025160</v>
+        <v>127025155</v>
       </c>
       <c r="B17" t="n">
-        <v>98470</v>
+        <v>98463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,16 +2289,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633926</v>
+        <v>633773</v>
       </c>
       <c r="R17" t="n">
-        <v>6963802</v>
+        <v>6964115</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,37 +2389,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127025156</v>
+        <v>127025170</v>
       </c>
       <c r="B18" t="n">
-        <v>98436</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633678</v>
+        <v>634032</v>
       </c>
       <c r="R18" t="n">
-        <v>6964104</v>
+        <v>6963951</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2458,22 +2458,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>TvÃ¥ individer i luven pÃ¥ varandra.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2500,37 +2505,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127025170</v>
+        <v>127025156</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2539,13 +2544,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>634032</v>
+        <v>633678</v>
       </c>
       <c r="R19" t="n">
-        <v>6963951</v>
+        <v>6964104</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2569,27 +2574,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>TvÃ¥ individer i luven pÃ¥ varandra.</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,7 +2619,7 @@
         <v>127025158</v>
       </c>
       <c r="B20" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>127025161</v>
       </c>
       <c r="B21" t="n">
-        <v>88722</v>
+        <v>88728</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>127025165</v>
       </c>
       <c r="B27" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -2051,37 +2051,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127025167</v>
+        <v>127025155</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>98463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633769</v>
+        <v>633773</v>
       </c>
       <c r="R15" t="n">
-        <v>6963779</v>
+        <v>6964115</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2135,12 +2135,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>FÃ¤rska ringhack</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2167,32 +2162,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127025160</v>
+        <v>127025167</v>
       </c>
       <c r="B16" t="n">
-        <v>98476</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2206,13 +2201,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633926</v>
+        <v>633769</v>
       </c>
       <c r="R16" t="n">
-        <v>6963802</v>
+        <v>6963779</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,7 +2236,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2251,7 +2246,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>FÃ¤rska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025155</v>
+        <v>127025160</v>
       </c>
       <c r="B17" t="n">
-        <v>98463</v>
+        <v>98476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,16 +2289,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633773</v>
+        <v>633926</v>
       </c>
       <c r="R17" t="n">
-        <v>6964115</v>
+        <v>6963802</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,37 +2389,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127025170</v>
+        <v>127025156</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>634032</v>
+        <v>633678</v>
       </c>
       <c r="R18" t="n">
-        <v>6963951</v>
+        <v>6964104</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2458,27 +2458,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>TvÃ¥ individer i luven pÃ¥ varandra.</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,37 +2500,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127025156</v>
+        <v>127025170</v>
       </c>
       <c r="B19" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2544,13 +2539,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633678</v>
+        <v>634032</v>
       </c>
       <c r="R19" t="n">
-        <v>6964104</v>
+        <v>6963951</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2574,22 +2569,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>TvÃ¥ individer i luven pÃ¥ varandra.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2727,10 +2727,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127025161</v>
+        <v>127025311</v>
       </c>
       <c r="B21" t="n">
-        <v>88728</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,41 +2738,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>GÃ¥ltjÃ¤rn, Ång</t>
+          <t>Skälansjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633930</v>
+        <v>633851</v>
       </c>
       <c r="R21" t="n">
-        <v>6963796</v>
+        <v>6963748</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2796,22 +2792,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2838,7 +2829,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127025311</v>
+        <v>127025310</v>
       </c>
       <c r="B22" t="n">
         <v>57657</v>
@@ -2873,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633851</v>
+        <v>633825</v>
       </c>
       <c r="R22" t="n">
-        <v>6963748</v>
+        <v>6963994</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2904,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska + äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127025310</v>
+        <v>127025161</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>88728</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,37 +2942,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skälansjön, Ång</t>
+          <t>GÃ¥ltjÃ¤rn, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633825</v>
+        <v>633930</v>
       </c>
       <c r="R23" t="n">
-        <v>6963994</v>
+        <v>6963796</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3005,17 +3000,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska + äldre ringhack på tall</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127025155</v>
+        <v>127025160</v>
       </c>
       <c r="B15" t="n">
-        <v>98463</v>
+        <v>98476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,16 +2062,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633773</v>
+        <v>633926</v>
       </c>
       <c r="R15" t="n">
-        <v>6964115</v>
+        <v>6963802</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,37 +2162,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127025167</v>
+        <v>127025155</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>98463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2201,13 +2201,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633769</v>
+        <v>633773</v>
       </c>
       <c r="R16" t="n">
-        <v>6963779</v>
+        <v>6964115</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2246,12 +2246,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>FÃ¤rska ringhack</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,32 +2273,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025160</v>
+        <v>127025167</v>
       </c>
       <c r="B17" t="n">
-        <v>98476</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2317,13 +2312,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633926</v>
+        <v>633769</v>
       </c>
       <c r="R17" t="n">
-        <v>6963802</v>
+        <v>6963779</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2347,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2357,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>FÃ¤rska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2727,10 +2727,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127025311</v>
+        <v>127025161</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>88728</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,37 +2738,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skälansjön, Ång</t>
+          <t>GÃ¥ltjÃ¤rn, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633851</v>
+        <v>633930</v>
       </c>
       <c r="R21" t="n">
-        <v>6963748</v>
+        <v>6963796</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2792,17 +2796,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,7 +2838,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127025310</v>
+        <v>127025311</v>
       </c>
       <c r="B22" t="n">
         <v>57657</v>
@@ -2864,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633825</v>
+        <v>633851</v>
       </c>
       <c r="R22" t="n">
-        <v>6963994</v>
+        <v>6963748</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2904,7 +2913,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska + äldre ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2931,10 +2940,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127025161</v>
+        <v>127025310</v>
       </c>
       <c r="B23" t="n">
-        <v>88728</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,41 +2951,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>GÃ¥ltjÃ¤rn, Ång</t>
+          <t>Skälansjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633930</v>
+        <v>633825</v>
       </c>
       <c r="R23" t="n">
-        <v>6963796</v>
+        <v>6963994</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3000,22 +3005,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska + äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>127025164</v>
       </c>
       <c r="B10" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>127025162</v>
       </c>
       <c r="B11" t="n">
-        <v>88728</v>
+        <v>88729</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>127025154</v>
       </c>
       <c r="B13" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>127025163</v>
       </c>
       <c r="B14" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127025160</v>
+        <v>127025167</v>
       </c>
       <c r="B15" t="n">
-        <v>98476</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633926</v>
+        <v>633769</v>
       </c>
       <c r="R15" t="n">
-        <v>6963802</v>
+        <v>6963779</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2135,7 +2135,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>FÃ¤rska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127025155</v>
+        <v>127025160</v>
       </c>
       <c r="B16" t="n">
-        <v>98463</v>
+        <v>98477</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,16 +2178,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2192,7 +2197,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2201,13 +2206,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633773</v>
+        <v>633926</v>
       </c>
       <c r="R16" t="n">
-        <v>6964115</v>
+        <v>6963802</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2236,7 +2241,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2246,7 +2251,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,37 +2278,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025167</v>
+        <v>127025155</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>98464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2312,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633769</v>
+        <v>633773</v>
       </c>
       <c r="R17" t="n">
-        <v>6963779</v>
+        <v>6964115</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2347,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2357,12 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>FÃ¤rska ringhack</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,37 +2389,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127025156</v>
+        <v>127025170</v>
       </c>
       <c r="B18" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633678</v>
+        <v>634032</v>
       </c>
       <c r="R18" t="n">
-        <v>6964104</v>
+        <v>6963951</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2458,22 +2458,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>TvÃ¥ individer i luven pÃ¥ varandra.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2500,37 +2505,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127025170</v>
+        <v>127025156</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2539,13 +2544,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>634032</v>
+        <v>633678</v>
       </c>
       <c r="R19" t="n">
-        <v>6963951</v>
+        <v>6964104</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2569,27 +2574,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>TvÃ¥ individer i luven pÃ¥ varandra.</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,7 +2619,7 @@
         <v>127025158</v>
       </c>
       <c r="B20" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>127025161</v>
       </c>
       <c r="B21" t="n">
-        <v>88728</v>
+        <v>88729</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>127025165</v>
       </c>
       <c r="B27" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -1713,32 +1713,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127025168</v>
+        <v>127025154</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>98477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633757</v>
+        <v>633966</v>
       </c>
       <c r="R12" t="n">
-        <v>6963816</v>
+        <v>6963757</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1797,12 +1797,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ã„ldre ringhack pÃ¥ tvÃ¥ tallar</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,32 +1824,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127025154</v>
+        <v>127025168</v>
       </c>
       <c r="B13" t="n">
-        <v>98477</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1868,10 +1863,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633966</v>
+        <v>633757</v>
       </c>
       <c r="R13" t="n">
-        <v>6963757</v>
+        <v>6963816</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,7 +1898,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1913,7 +1908,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ã„ldre ringhack pÃ¥ tvÃ¥ tallar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2167,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127025160</v>
+        <v>127025155</v>
       </c>
       <c r="B16" t="n">
-        <v>98477</v>
+        <v>98464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,16 +2178,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633926</v>
+        <v>633773</v>
       </c>
       <c r="R16" t="n">
-        <v>6963802</v>
+        <v>6964115</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025155</v>
+        <v>127025160</v>
       </c>
       <c r="B17" t="n">
-        <v>98464</v>
+        <v>98477</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,16 +2289,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633773</v>
+        <v>633926</v>
       </c>
       <c r="R17" t="n">
-        <v>6964115</v>
+        <v>6963802</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2838,7 +2838,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127025311</v>
+        <v>127025310</v>
       </c>
       <c r="B22" t="n">
         <v>57657</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633851</v>
+        <v>633825</v>
       </c>
       <c r="R22" t="n">
-        <v>6963748</v>
+        <v>6963994</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska + äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,7 +2940,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127025310</v>
+        <v>127025311</v>
       </c>
       <c r="B23" t="n">
         <v>57657</v>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633825</v>
+        <v>633851</v>
       </c>
       <c r="R23" t="n">
-        <v>6963994</v>
+        <v>6963748</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska + äldre ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127025167</v>
+        <v>127025160</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>98477</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633769</v>
+        <v>633926</v>
       </c>
       <c r="R15" t="n">
-        <v>6963779</v>
+        <v>6963802</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2135,12 +2135,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>FÃ¤rska ringhack</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,32 +2273,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025160</v>
+        <v>127025167</v>
       </c>
       <c r="B17" t="n">
-        <v>98477</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2317,13 +2312,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633926</v>
+        <v>633769</v>
       </c>
       <c r="R17" t="n">
-        <v>6963802</v>
+        <v>6963779</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2347,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2357,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>FÃ¤rska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2838,7 +2838,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127025310</v>
+        <v>127025311</v>
       </c>
       <c r="B22" t="n">
         <v>57657</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633825</v>
+        <v>633851</v>
       </c>
       <c r="R22" t="n">
-        <v>6963994</v>
+        <v>6963748</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska + äldre ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,7 +2940,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127025311</v>
+        <v>127025310</v>
       </c>
       <c r="B23" t="n">
         <v>57657</v>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633851</v>
+        <v>633825</v>
       </c>
       <c r="R23" t="n">
-        <v>6963748</v>
+        <v>6963994</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska + äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -1713,32 +1713,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127025154</v>
+        <v>127025168</v>
       </c>
       <c r="B12" t="n">
-        <v>98477</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633966</v>
+        <v>633757</v>
       </c>
       <c r="R12" t="n">
-        <v>6963757</v>
+        <v>6963816</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1797,7 +1797,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ã„ldre ringhack pÃ¥ tvÃ¥ tallar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,32 +1829,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127025168</v>
+        <v>127025154</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>98477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1863,10 +1868,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633757</v>
+        <v>633966</v>
       </c>
       <c r="R13" t="n">
-        <v>6963816</v>
+        <v>6963757</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,7 +1903,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1908,12 +1913,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ã„ldre ringhack pÃ¥ tvÃ¥ tallar</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>127025164</v>
       </c>
       <c r="B10" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>127025162</v>
       </c>
       <c r="B11" t="n">
-        <v>88729</v>
+        <v>88733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>127025168</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>127025154</v>
       </c>
       <c r="B13" t="n">
-        <v>98477</v>
+        <v>98481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>127025163</v>
       </c>
       <c r="B14" t="n">
-        <v>98477</v>
+        <v>98481</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127025160</v>
+        <v>127025167</v>
       </c>
       <c r="B15" t="n">
-        <v>98477</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633926</v>
+        <v>633769</v>
       </c>
       <c r="R15" t="n">
-        <v>6963802</v>
+        <v>6963779</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2135,7 +2135,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>FÃ¤rska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127025155</v>
+        <v>127025160</v>
       </c>
       <c r="B16" t="n">
-        <v>98464</v>
+        <v>98481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,16 +2178,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2192,7 +2197,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2201,13 +2206,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633773</v>
+        <v>633926</v>
       </c>
       <c r="R16" t="n">
-        <v>6964115</v>
+        <v>6963802</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2236,7 +2241,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2246,7 +2251,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,37 +2278,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025167</v>
+        <v>127025155</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2312,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633769</v>
+        <v>633773</v>
       </c>
       <c r="R17" t="n">
-        <v>6963779</v>
+        <v>6964115</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2347,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2357,12 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>FÃ¤rska ringhack</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2392,7 +2392,7 @@
         <v>127025170</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>127025156</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>127025158</v>
       </c>
       <c r="B20" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>127025161</v>
       </c>
       <c r="B21" t="n">
-        <v>88729</v>
+        <v>88733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,10 +2838,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127025311</v>
+        <v>127025310</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633851</v>
+        <v>633825</v>
       </c>
       <c r="R22" t="n">
-        <v>6963748</v>
+        <v>6963994</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska + äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,10 +2940,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127025310</v>
+        <v>127025311</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633825</v>
+        <v>633851</v>
       </c>
       <c r="R23" t="n">
-        <v>6963994</v>
+        <v>6963748</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska + äldre ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3045,7 +3045,7 @@
         <v>127025309</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>127025169</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>127025159</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>127025165</v>
       </c>
       <c r="B27" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>127025166</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -1713,32 +1713,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127025168</v>
+        <v>127025154</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>98481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633757</v>
+        <v>633966</v>
       </c>
       <c r="R12" t="n">
-        <v>6963816</v>
+        <v>6963757</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1797,12 +1797,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ã„ldre ringhack pÃ¥ tvÃ¥ tallar</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,32 +1824,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127025154</v>
+        <v>127025168</v>
       </c>
       <c r="B13" t="n">
-        <v>98481</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1868,10 +1863,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633966</v>
+        <v>633757</v>
       </c>
       <c r="R13" t="n">
-        <v>6963757</v>
+        <v>6963816</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,7 +1898,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1913,7 +1908,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ã„ldre ringhack pÃ¥ tvÃ¥ tallar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127025167</v>
+        <v>127025160</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>98481</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633769</v>
+        <v>633926</v>
       </c>
       <c r="R15" t="n">
-        <v>6963779</v>
+        <v>6963802</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2135,12 +2135,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>FÃ¤rska ringhack</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2167,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127025160</v>
+        <v>127025155</v>
       </c>
       <c r="B16" t="n">
-        <v>98481</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,16 +2173,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2197,7 +2192,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2206,13 +2201,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633926</v>
+        <v>633773</v>
       </c>
       <c r="R16" t="n">
-        <v>6963802</v>
+        <v>6964115</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,7 +2236,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2251,7 +2246,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,37 +2273,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025155</v>
+        <v>127025167</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2317,13 +2312,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633773</v>
+        <v>633769</v>
       </c>
       <c r="R17" t="n">
-        <v>6964115</v>
+        <v>6963779</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2347,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2357,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>FÃ¤rska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2838,7 +2838,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127025310</v>
+        <v>127025311</v>
       </c>
       <c r="B22" t="n">
         <v>57661</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633825</v>
+        <v>633851</v>
       </c>
       <c r="R22" t="n">
-        <v>6963994</v>
+        <v>6963748</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska + äldre ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,7 +2940,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127025311</v>
+        <v>127025310</v>
       </c>
       <c r="B23" t="n">
         <v>57661</v>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633851</v>
+        <v>633825</v>
       </c>
       <c r="R23" t="n">
-        <v>6963748</v>
+        <v>6963994</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska + äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -1713,32 +1713,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127025154</v>
+        <v>127025168</v>
       </c>
       <c r="B12" t="n">
-        <v>98481</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633966</v>
+        <v>633757</v>
       </c>
       <c r="R12" t="n">
-        <v>6963757</v>
+        <v>6963816</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1797,7 +1797,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ã„ldre ringhack pÃ¥ tvÃ¥ tallar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,32 +1829,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127025168</v>
+        <v>127025154</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>98481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1863,10 +1868,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633757</v>
+        <v>633966</v>
       </c>
       <c r="R13" t="n">
-        <v>6963816</v>
+        <v>6963757</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,7 +1903,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1908,12 +1913,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ã„ldre ringhack pÃ¥ tvÃ¥ tallar</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2162,37 +2162,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127025155</v>
+        <v>127025167</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2201,13 +2201,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633773</v>
+        <v>633769</v>
       </c>
       <c r="R16" t="n">
-        <v>6964115</v>
+        <v>6963779</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2246,7 +2246,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>FÃ¤rska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,37 +2278,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025167</v>
+        <v>127025155</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2312,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633769</v>
+        <v>633773</v>
       </c>
       <c r="R17" t="n">
-        <v>6963779</v>
+        <v>6964115</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2347,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2357,12 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>FÃ¤rska ringhack</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -2162,37 +2162,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127025167</v>
+        <v>127025155</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2201,13 +2201,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633769</v>
+        <v>633773</v>
       </c>
       <c r="R16" t="n">
-        <v>6963779</v>
+        <v>6964115</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2246,12 +2246,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>FÃ¤rska ringhack</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,37 +2273,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025155</v>
+        <v>127025167</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2317,13 +2312,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633773</v>
+        <v>633769</v>
       </c>
       <c r="R17" t="n">
-        <v>6964115</v>
+        <v>6963779</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2347,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2357,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>FÃ¤rska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -1713,32 +1713,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127025168</v>
+        <v>127025154</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>98482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633757</v>
+        <v>633966</v>
       </c>
       <c r="R12" t="n">
-        <v>6963816</v>
+        <v>6963757</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1797,12 +1797,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ã„ldre ringhack pÃ¥ tvÃ¥ tallar</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,32 +1824,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127025154</v>
+        <v>127025168</v>
       </c>
       <c r="B13" t="n">
-        <v>98481</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1868,10 +1863,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633966</v>
+        <v>633757</v>
       </c>
       <c r="R13" t="n">
-        <v>6963757</v>
+        <v>6963816</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,7 +1898,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1913,7 +1908,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ã„ldre ringhack pÃ¥ tvÃ¥ tallar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1943,7 +1943,7 @@
         <v>127025163</v>
       </c>
       <c r="B14" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127025160</v>
+        <v>127025167</v>
       </c>
       <c r="B15" t="n">
-        <v>98481</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633926</v>
+        <v>633769</v>
       </c>
       <c r="R15" t="n">
-        <v>6963802</v>
+        <v>6963779</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2135,7 +2135,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>FÃ¤rska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2165,7 +2170,7 @@
         <v>127025155</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,32 +2278,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025167</v>
+        <v>127025160</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>98482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2312,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633769</v>
+        <v>633926</v>
       </c>
       <c r="R17" t="n">
-        <v>6963779</v>
+        <v>6963802</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2347,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2357,12 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>FÃ¤rska ringhack</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,7 +2508,7 @@
         <v>127025156</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>127025158</v>
       </c>
       <c r="B20" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127025161</v>
+        <v>127025311</v>
       </c>
       <c r="B21" t="n">
-        <v>88733</v>
+        <v>57661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,41 +2738,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>GÃ¥ltjÃ¤rn, Ång</t>
+          <t>Skälansjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633930</v>
+        <v>633851</v>
       </c>
       <c r="R21" t="n">
-        <v>6963796</v>
+        <v>6963748</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2796,22 +2792,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2838,7 +2829,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127025311</v>
+        <v>127025310</v>
       </c>
       <c r="B22" t="n">
         <v>57661</v>
@@ -2873,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633851</v>
+        <v>633825</v>
       </c>
       <c r="R22" t="n">
-        <v>6963748</v>
+        <v>6963994</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2904,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska + äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127025310</v>
+        <v>127025161</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>88733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,37 +2942,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skälansjön, Ång</t>
+          <t>GÃ¥ltjÃ¤rn, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633825</v>
+        <v>633930</v>
       </c>
       <c r="R23" t="n">
-        <v>6963994</v>
+        <v>6963796</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3005,17 +3000,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska + äldre ringhack på tall</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -2829,10 +2829,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127025310</v>
+        <v>127025161</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>88733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,37 +2840,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skälansjön, Ång</t>
+          <t>GÃ¥ltjÃ¤rn, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633825</v>
+        <v>633930</v>
       </c>
       <c r="R22" t="n">
-        <v>6963994</v>
+        <v>6963796</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2894,17 +2898,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska + äldre ringhack på tall</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2931,10 +2940,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127025161</v>
+        <v>127025310</v>
       </c>
       <c r="B23" t="n">
-        <v>88733</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,41 +2951,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>GÃ¥ltjÃ¤rn, Ång</t>
+          <t>Skälansjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633930</v>
+        <v>633825</v>
       </c>
       <c r="R23" t="n">
-        <v>6963796</v>
+        <v>6963994</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3000,22 +3005,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska + äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>127025164</v>
       </c>
       <c r="B10" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>127025162</v>
       </c>
       <c r="B11" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>127025154</v>
       </c>
       <c r="B12" t="n">
-        <v>98482</v>
+        <v>98484</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>127025168</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>127025163</v>
       </c>
       <c r="B14" t="n">
-        <v>98482</v>
+        <v>98484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>127025167</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127025155</v>
+        <v>127025160</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>98484</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,16 +2178,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633773</v>
+        <v>633926</v>
       </c>
       <c r="R16" t="n">
-        <v>6964115</v>
+        <v>6963802</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025160</v>
+        <v>127025155</v>
       </c>
       <c r="B17" t="n">
-        <v>98482</v>
+        <v>98471</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,16 +2289,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633926</v>
+        <v>633773</v>
       </c>
       <c r="R17" t="n">
-        <v>6963802</v>
+        <v>6964115</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2392,7 +2392,7 @@
         <v>127025170</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>127025156</v>
       </c>
       <c r="B19" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>127025158</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>127025311</v>
       </c>
       <c r="B21" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127025161</v>
+        <v>127025310</v>
       </c>
       <c r="B22" t="n">
-        <v>88733</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,41 +2840,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>GÃ¥ltjÃ¤rn, Ång</t>
+          <t>Skälansjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633930</v>
+        <v>633825</v>
       </c>
       <c r="R22" t="n">
-        <v>6963796</v>
+        <v>6963994</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2898,22 +2894,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska + äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127025310</v>
+        <v>127025161</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>88735</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,37 +2942,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skälansjön, Ång</t>
+          <t>GÃ¥ltjÃ¤rn, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633825</v>
+        <v>633930</v>
       </c>
       <c r="R23" t="n">
-        <v>6963994</v>
+        <v>6963796</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3005,17 +3000,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska + äldre ringhack på tall</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3045,7 +3045,7 @@
         <v>127025309</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>127025169</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>127025159</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>127025165</v>
       </c>
       <c r="B27" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>127025166</v>
       </c>
       <c r="B28" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -2727,10 +2727,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127025311</v>
+        <v>127025161</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>88735</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,37 +2738,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skälansjön, Ång</t>
+          <t>GÃ¥ltjÃ¤rn, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633851</v>
+        <v>633930</v>
       </c>
       <c r="R21" t="n">
-        <v>6963748</v>
+        <v>6963796</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2792,17 +2796,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,7 +2838,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127025310</v>
+        <v>127025311</v>
       </c>
       <c r="B22" t="n">
         <v>57663</v>
@@ -2864,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633825</v>
+        <v>633851</v>
       </c>
       <c r="R22" t="n">
-        <v>6963994</v>
+        <v>6963748</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2904,7 +2913,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska + äldre ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2931,10 +2940,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127025161</v>
+        <v>127025310</v>
       </c>
       <c r="B23" t="n">
-        <v>88735</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,41 +2951,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>GÃ¥ltjÃ¤rn, Ång</t>
+          <t>Skälansjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633930</v>
+        <v>633825</v>
       </c>
       <c r="R23" t="n">
-        <v>6963796</v>
+        <v>6963994</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3000,22 +3005,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska + äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -1713,32 +1713,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127025154</v>
+        <v>127025168</v>
       </c>
       <c r="B12" t="n">
-        <v>98484</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633966</v>
+        <v>633757</v>
       </c>
       <c r="R12" t="n">
-        <v>6963757</v>
+        <v>6963816</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1797,7 +1797,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ã„ldre ringhack pÃ¥ tvÃ¥ tallar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,32 +1829,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127025168</v>
+        <v>127025154</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>98484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1863,10 +1868,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633757</v>
+        <v>633966</v>
       </c>
       <c r="R13" t="n">
-        <v>6963816</v>
+        <v>6963757</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,7 +1903,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1908,12 +1913,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ã„ldre ringhack pÃ¥ tvÃ¥ tallar</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2167,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127025160</v>
+        <v>127025155</v>
       </c>
       <c r="B16" t="n">
-        <v>98484</v>
+        <v>98471</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,16 +2178,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633926</v>
+        <v>633773</v>
       </c>
       <c r="R16" t="n">
-        <v>6963802</v>
+        <v>6964115</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025155</v>
+        <v>127025160</v>
       </c>
       <c r="B17" t="n">
-        <v>98471</v>
+        <v>98484</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,16 +2289,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633773</v>
+        <v>633926</v>
       </c>
       <c r="R17" t="n">
-        <v>6964115</v>
+        <v>6963802</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>127025164</v>
       </c>
       <c r="B10" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>127025162</v>
       </c>
       <c r="B11" t="n">
-        <v>88735</v>
+        <v>88741</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>127025154</v>
       </c>
       <c r="B13" t="n">
-        <v>98484</v>
+        <v>98490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>127025163</v>
       </c>
       <c r="B14" t="n">
-        <v>98484</v>
+        <v>98490</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,37 +2051,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127025167</v>
+        <v>127025155</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>98477</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633769</v>
+        <v>633773</v>
       </c>
       <c r="R15" t="n">
-        <v>6963779</v>
+        <v>6964115</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2135,12 +2135,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>FÃ¤rska ringhack</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2167,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127025155</v>
+        <v>127025160</v>
       </c>
       <c r="B16" t="n">
-        <v>98471</v>
+        <v>98490</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,16 +2173,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2197,7 +2192,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2206,13 +2201,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633773</v>
+        <v>633926</v>
       </c>
       <c r="R16" t="n">
-        <v>6964115</v>
+        <v>6963802</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,7 +2236,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2251,7 +2246,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,32 +2273,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025160</v>
+        <v>127025167</v>
       </c>
       <c r="B17" t="n">
-        <v>98484</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2317,13 +2312,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633926</v>
+        <v>633769</v>
       </c>
       <c r="R17" t="n">
-        <v>6963802</v>
+        <v>6963779</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2347,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2357,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>FÃ¤rska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,7 +2508,7 @@
         <v>127025156</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>127025158</v>
       </c>
       <c r="B20" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>127025161</v>
       </c>
       <c r="B21" t="n">
-        <v>88735</v>
+        <v>88741</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>127025165</v>
       </c>
       <c r="B27" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>127025164</v>
       </c>
       <c r="B10" t="n">
-        <v>91338</v>
+        <v>91319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>127025162</v>
       </c>
       <c r="B11" t="n">
-        <v>88741</v>
+        <v>88722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>127025168</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>127025154</v>
       </c>
       <c r="B13" t="n">
-        <v>98490</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>127025163</v>
       </c>
       <c r="B14" t="n">
-        <v>98490</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>127025155</v>
       </c>
       <c r="B15" t="n">
-        <v>98477</v>
+        <v>98457</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127025160</v>
+        <v>127025167</v>
       </c>
       <c r="B16" t="n">
-        <v>98490</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2201,13 +2201,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633926</v>
+        <v>633769</v>
       </c>
       <c r="R16" t="n">
-        <v>6963802</v>
+        <v>6963779</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2246,7 +2246,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>FÃ¤rska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,32 +2278,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025167</v>
+        <v>127025160</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>98470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2312,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633769</v>
+        <v>633926</v>
       </c>
       <c r="R17" t="n">
-        <v>6963779</v>
+        <v>6963802</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2347,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2357,12 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>FÃ¤rska ringhack</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,37 +2389,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127025170</v>
+        <v>127025156</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>98436</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>634032</v>
+        <v>633678</v>
       </c>
       <c r="R18" t="n">
-        <v>6963951</v>
+        <v>6964104</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2458,27 +2458,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>TvÃ¥ individer i luven pÃ¥ varandra.</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,37 +2500,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127025156</v>
+        <v>127025170</v>
       </c>
       <c r="B19" t="n">
-        <v>98456</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2544,13 +2539,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633678</v>
+        <v>634032</v>
       </c>
       <c r="R19" t="n">
-        <v>6964104</v>
+        <v>6963951</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2574,22 +2569,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>TvÃ¥ individer i luven pÃ¥ varandra.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,7 +2619,7 @@
         <v>127025158</v>
       </c>
       <c r="B20" t="n">
-        <v>98373</v>
+        <v>98353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>127025161</v>
       </c>
       <c r="B21" t="n">
-        <v>88741</v>
+        <v>88722</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>127025311</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>127025310</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>127025309</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>127025169</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>127025159</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>127025165</v>
       </c>
       <c r="B27" t="n">
-        <v>91792</v>
+        <v>91773</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>127025166</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>127025164</v>
       </c>
       <c r="B10" t="n">
-        <v>91319</v>
+        <v>91338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>127025162</v>
       </c>
       <c r="B11" t="n">
-        <v>88722</v>
+        <v>88741</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>127025168</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>127025154</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>127025163</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>98490</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>127025155</v>
       </c>
       <c r="B15" t="n">
-        <v>98457</v>
+        <v>98477</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127025167</v>
+        <v>127025160</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>98490</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2201,13 +2201,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633769</v>
+        <v>633926</v>
       </c>
       <c r="R16" t="n">
-        <v>6963779</v>
+        <v>6963802</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2246,12 +2246,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>FÃ¤rska ringhack</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,32 +2273,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127025160</v>
+        <v>127025167</v>
       </c>
       <c r="B17" t="n">
-        <v>98470</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2317,13 +2312,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633926</v>
+        <v>633769</v>
       </c>
       <c r="R17" t="n">
-        <v>6963802</v>
+        <v>6963779</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2347,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2357,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>FÃ¤rska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,37 +2389,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127025156</v>
+        <v>127025170</v>
       </c>
       <c r="B18" t="n">
-        <v>98436</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633678</v>
+        <v>634032</v>
       </c>
       <c r="R18" t="n">
-        <v>6964104</v>
+        <v>6963951</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2458,22 +2458,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>TvÃ¥ individer i luven pÃ¥ varandra.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2500,37 +2505,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127025170</v>
+        <v>127025156</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>98456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2539,13 +2544,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>634032</v>
+        <v>633678</v>
       </c>
       <c r="R19" t="n">
-        <v>6963951</v>
+        <v>6964104</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2569,27 +2574,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>TvÃ¥ individer i luven pÃ¥ varandra.</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,7 +2619,7 @@
         <v>127025158</v>
       </c>
       <c r="B20" t="n">
-        <v>98353</v>
+        <v>98373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>127025161</v>
       </c>
       <c r="B21" t="n">
-        <v>88722</v>
+        <v>88741</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>127025311</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>127025310</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>127025309</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>127025169</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>127025159</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>127025165</v>
       </c>
       <c r="B27" t="n">
-        <v>91773</v>
+        <v>91792</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>127025166</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2025 artfynd.xlsx
+++ b/artfynd/A 18689-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119269215</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025161</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025162</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119269216</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025164</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119269209</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1393,6 +1428,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119269208</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025165</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1601,6 +1646,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119269210</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119269211</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1795,6 +1850,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119269212</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1892,6 +1952,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119269213</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2008,6 +2073,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025159</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2124,6 +2194,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025166</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2240,6 +2315,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025167</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2356,6 +2436,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025168</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2472,6 +2557,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025169</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2588,6 +2678,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025170</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2690,6 +2785,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025309</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025310</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2894,6 +2999,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025311</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2996,6 +3106,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025312</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3107,6 +3222,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025158</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3218,6 +3338,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025154</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3329,6 +3454,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025160</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3440,6 +3570,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025163</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3551,6 +3686,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025156</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3662,8 +3802,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025155</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>